--- a/output/pdf_financials_xlsx/MER.xlsx
+++ b/output/pdf_financials_xlsx/MER.xlsx
@@ -6153,7 +6153,7 @@
         <v>0</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>7.7</v>
+        <v>15.4</v>
       </c>
       <c r="N91" s="3" t="n">
         <v>0</v>

--- a/output/pdf_financials_xlsx/MER.xlsx
+++ b/output/pdf_financials_xlsx/MER.xlsx
@@ -2921,10 +2921,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.253324</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>11.145486</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>11.145486</v>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.253324</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>11.145486</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>11.145486</v>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.253324</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>11.65383</v>
+        <v>0.508344</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.508344</v>
@@ -44966,7 +44966,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E386" s="5" t="n">
